--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0021.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0021.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Divine Giọng nói</t>
+          <t>Thiên Âm</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Imagination</t>
+          <t>Trí Tưởng Tượng</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Beyond Imagination</t>
+          <t>Vượt Quá Tưởng Tượng</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Moldable Crystal</t>
+          <t>Pha Lê Tạo Hình</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Substance</t>
+          <t>Chất liệu</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Deconstruction</t>
+          <t>Phân rã</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Dispersion</t>
+          <t>Phân tán</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Budding Mode</t>
+          <t>Chế Độ Nảy Mầm</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Collapsed Core</t>
+          <t>Lõi Sụp Đổ</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Stellarealm</t>
+          <t>Vực Tinh Tú</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Outer Stellarealm</t>
+          <t>Vùng Ngoài Hư Không Tinh Tú</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Intuition</t>
+          <t>Trực giác</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Phatasmic Imprint</t>
+          <t>Dấu Ấn Ảo Ảnh</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Afflatus</t>
+          <t>Cảm Hứng</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Sinner's Mark</t>
+          <t>Dấu Ấn Tội Nhân</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Judgement Points</t>
+          <t>Điểm Phán Xét</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Qingloong Mode</t>
+          <t>Chế Độ Thanh Long</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Resolve</t>
+          <t>Sự Quyết Đoán</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Concentration</t>
+          <t>Tập Trung</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Dark Surge</t>
+          <t>Sóng Bóng Tối</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Ice Prism</t>
+          <t>Lăng Kính Băng</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Ice Thorn</t>
+          <t>Gai Băng</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Glacier</t>
+          <t>Băng Hà</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Burning Rhapsody</t>
+          <t>Khúc Rhapsody Cháy Bỏng</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Ruby Blossom</t>
+          <t>Hoa Hồng Đá</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Incinerating Will</t>
+          <t>Ý Chí Thiêu Đốt</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Thermobaric Bullets</t>
+          <t>Đạn Nhiệt Áp</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Yellow Light Mode</t>
+          <t>Chế Độ Ánh Sáng Vàng</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Red Light Mode</t>
+          <t>Chế Độ Ánh Sáng Đỏ</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Lucky Draw</t>
+          <t>Rút Thăm May Mắn</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Antique</t>
+          <t>Đồ cổ</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Rocksteady Shield</t>
+          <t>Khiên Vững Chãi</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Mist</t>
+          <t>Sương mù</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Gate of Quandary</t>
+          <t>Cổng Băn Khoăn</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Tuyệt vời!</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Aflame</t>
+          <t>Bốc Cháy</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Theatrical Moment</t>
+          <t>Khoảnh Khắc Sân Khấu</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Waves Cổ Vũ</t>
+          <t>Làn Sóng Cổ Vũ</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Mirage</t>
+          <t>Ảo Ảnh</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Hazy Dream</t>
+          <t>Giấc Mơ Mơ Hồ</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Windstring</t>
+          <t>Dây Gió</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Striding Lion</t>
+          <t>Sư Tử Bước Đi</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Ensemble Sylph</t>
+          <t>Dàn Nhạc Sylph</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Solo Concert</t>
+          <t>Buổi Hòa Nhạc Đơn Ca</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Musical Essence</t>
+          <t>Tinh Hoa Âm Nhạc</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Vibration Strength</t>
+          <t>Cường Độ Rung Động</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Redundant Energy</t>
+          <t>Năng Lượng Dư Thừa</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Inferno Mode</t>
+          <t>Chế Độ Hỏa Ngục</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Blaze</t>
+          <t>Lửa Thiêu</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Rabelle's Curve</t>
+          <t>Đường Cong Rabelle</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Congenital Resonator</t>
+          <t>Resonator Bẩm Sinh</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Mutant Resonator</t>
+          <t>Resonator Đột Biến</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Natural Resonator</t>
+          <t>Resonator Tự Nhiên</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Induced Resonator</t>
+          <t>Resonator Cảm Ứng</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Tacet Mark</t>
+          <t>Dấu Tacet</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Overclocking</t>
+          <t>Đang Quá Tải</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Threnodian</t>
+          <t>Người Threnody</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Lament</t>
+          <t>Lời Than Vãn</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Remnant Energy</t>
+          <t>Dư Năng Lượng</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Waveworn Phenomena</t>
+          <t>Hiện Tượng Sóng Mòn</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Discord</t>
+          <t>Tacet Discord</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Magistrate</t>
+          <t>Quan Án</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Ministry of Development</t>
+          <t>Bộ Phát Triển</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Midnight Rangers</t>
+          <t>Kỵ Sĩ Bóng Đêm</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Patroller</t>
+          <t>Nhân Viên Tuần Tra</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Patrol Station</t>
+          <t>Trạm Tuần Tra</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Lollo Logistics</t>
+          <t>Lollo Hậu Cần</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Cathedral of Mercury</t>
+          <t>Nhà Thờ Mercury</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Giáo Đoàn Vực Sâu</t>
+          <t>Lệnh của Vực Sâu</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Acolyte</t>
+          <t>Tín Đồ</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Imperator</t>
+          <t>Đại Đế</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Cetus the Tidebreaker</t>
+          <t>Cetus Kẻ Phá Thủy Triều</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Averardo Bank</t>
+          <t>Ngân Hàng Averardo</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Troupe of Fools</t>
+          <t>Đoàn Hội Ngớ Ngẩn</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Modulator</t>
+          <t>Điều Biến Giả</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Jinzhou Patroller</t>
+          <t>Tuần Tra Viên Jinzhou</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Overdash</t>
+          <t>Bay vượt tốc</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Leihuangquan</t>
+          <t>Lôi Hoàng Quyền</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Loong Whiskers Crisp</t>
+          <t>Bánh Giòn Râu Rồng</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Thư viện Hoàng Gia</t>
+          <t>Thư Viện Hoàng Gia</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Magistrate of Jinzhou</t>
+          <t>Chấp Pháp thành Jinzhou</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Illusory Dream</t>
+          <t>Giấc Mộng Ảo</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Velvet Dream</t>
+          <t>Giấc Mơ Nhung</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Magic Box</t>
+          <t>Hộp Ảo Thuật</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Magistrate's Bodyguard</t>
+          <t>Vệ Binh của Chấp Pháp</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Golden Anthem</t>
+          <t>Khúc Ca Hoàng Kim</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Shelter Home</t>
+          <t>Nơi Trú Ẩn</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Master Xuanmiao</t>
+          <t>Sư phụ Xuanmiao</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Jinzhou Counselor</t>
+          <t>Cố Vấn Jinzhou</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Liondance Troupe</t>
+          <t>Đoàn Múa Lân</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Liondance</t>
+          <t>Múa Sư Tử</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Lion Head</t>
+          <t>Đầu Sư Tử</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Starflower</t>
+          <t>Hoa Sao</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Fengyiquan</t>
+          <t>Phong Ý Quyền</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Ngân Hàng</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Ngõ Tối</t>
+          <t>Black Alley</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>The Second Dark Tide</t>
+          <t>Làn Sóng Bóng Tối Thứ Hai</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Carnevale Event A Decade Ago</t>
+          <t>Carnevale Một Thập Kỷ Trước</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Outrider</t>
+          <t>Kỵ Binh Tiền Tuyến</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Liên hoan phim Solaris</t>
+          <t>Liên hoan Điện ảnh Solaris</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Nightmare Discord</t>
+          <t>Tacet Discord Ác Mộng</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Ebony Gatekeeper</t>
+          <t>Người Gác Cổng Hắc Ám</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Ivory Doorkeeper</t>
+          <t>Người Gác Cổng Ngà</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Deep Water Zone</t>
+          <t>Khu Vực Nước Sâu</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Great Agon</t>
+          <t>Đại Khổ Luận</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Gryphon's Fortress</t>
+          <t>Pháo Đài Gryphon</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Heartpour</t>
+          <t>Tâm Hồng</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Priestess</t>
+          <t>Nữ tu sĩ</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Phát</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Copper Mirror</t>
+          <t>Gương Đồng</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>High Tide</t>
+          <t>Triều Cường</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Thung Lũng Glory</t>
+          <t>Thung Lũng Vinh Quang</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Border Mountains</t>
+          <t>Núi Biên Giới</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Gladiator</t>
+          <t>Đấu sĩ</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Echo Gladiating</t>
+          <t>Đấu Trường Cộng Hưởng</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Hero's Legacy Armor</t>
+          <t>Bộ Giáp Di Sản Anh Hùng</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Guardian Echo</t>
+          <t>Echo Người Bảo Vệ</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>House Silva</t>
+          <t>Gia Tộc Silva</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Senate</t>
+          <t>Thượng Nghị Viện</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Blightcloud</t>
+          <t>Mây Hắc Ám</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Cliffside Harbor</t>
+          <t>Cảng Cliffside</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Ready Stance</t>
+          <t>Tư thế sẵn sàng</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Pack Hunt</t>
+          <t>Săn Đoàn</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Burning Matchpoint</t>
+          <t>Điểm Hỏa Cháy</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Glory</t>
+          <t>Vinh Quang</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Conviction</t>
+          <t>Niềm Tin</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Heart of Virtue</t>
+          <t>Trái Tim Nhân Đức</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Mandate of Divinity</t>
+          <t>Thiên Mệnh</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Sức Mạnh Discord</t>
+          <t>Sức Mạnh Tacet Discord</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Kiếm Shadow Đức Hạnh</t>
+          <t>Kiếm Bóng Tối Đức Hạnh</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Kiếm Shadow Discord</t>
+          <t>Kiếm Bóng Tối Tacet Discord</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Kiếm Shadow Thần Thánh</t>
+          <t>Kiếm Bóng Tối Thần Thánh</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Dream of Gradation</t>
+          <t>Giấc Mộng Phân Tầng</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Dream of Devouring</t>
+          <t>Giấc Mộng Nuốt Chửng</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Giấc Mộng Trao đổi</t>
+          <t>Giấc Mộng Trao Đổi</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Dream of Integration</t>
+          <t>Giấc Mộng Hòa Nhập</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Dream of Connection</t>
+          <t>Giấc Mộng Kết Nối</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Gradation</t>
+          <t>Phân Cấp</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Devour</t>
+          <t>Nuốt chửng</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Exchange</t>
+          <t>Đổi</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Hợp Nhất</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Daily Coupon</t>
+          <t>Phiếu thưởng hàng ngày</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Dreamland Coupons</t>
+          <t>Phiếu Giấc Mơ</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Frequency Crystal</t>
+          <t>Pha Lê Tần Số</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Echo Recruitment</t>
+          <t>Tuyển Chọn Tần Số</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Item of Exchange</t>
+          <t>Vật phẩm trao đổi</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Rooted</t>
+          <t>Đã bén rễ</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Dream Block: Gravel</t>
+          <t>Khối Mộng: Sỏi Đá</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Dream Block: Ice Shards</t>
+          <t>Khối Mộng: Mảnh Băng</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Book of Prophecies</t>
+          <t>Sách Tiên Tri</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Hero of Heroes</t>
+          <t>Anh Hùng Trong Các Anh Hùng</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>The Lost Beyond</t>
+          <t>Vùng Đất Mất Tích</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Echo Brooder</t>
+          <t>Kẻ Ấp Ủ Echo</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Dark Tide</t>
+          <t>Thủy Triều Bóng Tối</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Retroact Rain</t>
+          <t>Mưa Hồi Quang</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Harbinger</t>
+          <t>Sứ Giả</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Beyond</t>
+          <t>Vượt Qua</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Threnodian's Gem</t>
+          <t>Ngọc Threnodian</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Figurine: Conductor</t>
+          <t>Mô hình: Nhạc Trưởng</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Fortune Bell</t>
+          <t>Chuông May Mắn</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Round Xoáy Giấc Mơ</t>
+          <t>Vòng Xoáy Giấc Mơ</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Dreamy Firework</t>
+          <t>Pháo Hoa Mộng Mơ</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Kaleidoscope</t>
+          <t>Kính Vạn Hoa</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Surprise Box</t>
+          <t>Hộp Bất Ngờ</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Clockwork Illuminator</t>
+          <t>Người Chiếu Sáng Cơ Khí</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Dreamscape Train</t>
+          <t>Đoàn Tàu Mộng Ảo</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Stamp Book</t>
+          <t>Sổ Tem</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Figurine: Clang Bang</t>
+          <t>Mô hình: Clang Bang</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Nổi Giận Trước Statue</t>
+          <t>Nổi Giận Trước Bức Tượng</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Basic Form</t>
+          <t>Bản Thể Cơ bản</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Dream Block: Obsidian</t>
+          <t>Khối Mộng: Hắc Diện Thạch</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Chop Chop</t>
+          <t>Nhanh lên nào</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Prism</t>
+          <t>Lăng Kính</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Adjacent</t>
+          <t>Lân cận</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Same Row</t>
+          <t>Cùng hàng</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Any Rarity</t>
+          <t>Độ Hiếm Bất Kỳ</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Questless Knight</t>
+          <t>Hiệp Sĩ Không Nhiệm Vụ</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Adjacent</t>
+          <t>Lân cận</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Fusion Cube</t>
+          <t>Khối Hợp Thể</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Dreamborne: Roseshroom</t>
+          <t>Dreamborne: Nấm Hồng Roseshroom</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Dream Block: Watermirror</t>
+          <t>Khối Mộng: Gương Nước</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Neon Tower</t>
+          <t>Tháp Neon</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Left Behind</t>
+          <t>Bị bỏ lại</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Longings</t>
+          <t>Khát Khao</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Irideglow Crystal</t>
+          <t>Pha lê Irideglow</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Startorch Academy</t>
+          <t>Học viện Startorch</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Void Storm</t>
+          <t>Bão Hư Không</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Spacetrek Collective</t>
+          <t>Tập Đoàn Spacetrek</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Namipon mất tích</t>
+          <t>Thiếu Namipon</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Keystone</t>
+          <t>Đá Chìa Khóa</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Stridergate</t>
+          <t>Cổng Bước Chân</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Seal of Flaming Sakura</t>
+          <t>Ấn Triện Sakura Rực Lửa</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
